--- a/src/shayda/client_data.xlsx
+++ b/src/shayda/client_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arriv\ws\client-product-dev\shayda\src\shayda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3757A790-4E61-4709-9CC5-12EDD3DC3641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D0B138-6C20-4CBE-BEB6-83E6E5C733E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1870" yWindow="960" windowWidth="20440" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44340" yWindow="3900" windowWidth="20445" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -72,8 +72,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -365,7 +368,7 @@
       <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
